--- a/output/pdf_financials_xlsx/IFA.xlsx
+++ b/output/pdf_financials_xlsx/IFA.xlsx
@@ -5897,34 +5897,34 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.036578</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.430687</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.567433</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.293619</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.768217</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.264746</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.675458</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.614722</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.185631000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.179614</v>
       </c>
     </row>
     <row r="93">
@@ -11274,7 +11274,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -17193,7 +17197,11 @@
           <t>Reserves (note 27)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IFA.xlsx
+++ b/output/pdf_financials_xlsx/IFA.xlsx
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>5.428068</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>6.042353</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>6.097935</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>5.258592</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>5.425859</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002103</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.052455</v>
+        <v>-0.054558</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.06229</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.052455</v>
+        <v>-0.054558</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.06229</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.040432</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.762608</v>
@@ -2481,40 +2481,40 @@
         <v>0.457131</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.006385</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.852016</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.260213</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.668425</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.542899</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.287548</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.160428</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.901718000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.944725</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.571744</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.058156</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.783334</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.040432</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.762608</v>
@@ -2597,40 +2597,40 @@
         <v>0.457131</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.006385</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.852016</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.260213</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.668425</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.542899</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.287548</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.160428</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.901718000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.944725</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.571744</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.058156</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>3.783334</v>
       </c>
     </row>
     <row r="37">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.043495</v>
+        <v>0.003063</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.296939</v>
@@ -3293,40 +3293,40 @@
         <v>0.243137</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.349746</v>
+        <v>0.343361</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.217483</v>
+        <v>0.365467</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.684105</v>
+        <v>0.423892</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.035036</v>
+        <v>0.366611</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.74525</v>
+        <v>0.202351</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.902994</v>
+        <v>0.615446</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.66039</v>
+        <v>4.499962</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>13.726591</v>
+        <v>4.824873</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.323253</v>
+        <v>5.378528</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.584863</v>
+        <v>1.013119</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.356027</v>
+        <v>1.297871</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>6.664058</v>
+        <v>2.880724</v>
       </c>
     </row>
     <row r="49">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -35749,7 +35749,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -40109,7 +40109,11 @@
           <t>Selling, general and administrative costs (note 17)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -41659,7 +41663,11 @@
           <t>Selling, general and administrative costs (note 16)</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -44560,7 +44568,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E373" s="5" t="n">

--- a/output/pdf_financials_xlsx/IFA.xlsx
+++ b/output/pdf_financials_xlsx/IFA.xlsx
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
@@ -7032,22 +7032,22 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.013484</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.007939999999999999</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.038671</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -30437,7 +30437,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
